--- a/esempio-prodotti.xlsx
+++ b/esempio-prodotti.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Listino" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Listino" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -61,12 +61,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -433,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:H33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -443,6 +446,7 @@
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
     <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="17" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -481,6 +485,11 @@
           <t>IVA %</t>
         </is>
       </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Codice a barre</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -510,6 +519,11 @@
       <c r="G2" s="3" t="n">
         <v>22</v>
       </c>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>2000000000015</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -539,6 +553,11 @@
       <c r="G3" s="3" t="n">
         <v>22</v>
       </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>2000000000022</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -568,6 +587,11 @@
       <c r="G4" s="3" t="n">
         <v>22</v>
       </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>2000000000039</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -597,6 +621,11 @@
       <c r="G5" s="3" t="n">
         <v>22</v>
       </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>2000000000046</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -626,6 +655,11 @@
       <c r="G6" s="3" t="n">
         <v>22</v>
       </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>2000000000053</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -655,6 +689,11 @@
       <c r="G7" s="3" t="n">
         <v>22</v>
       </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>2000000000060</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -684,6 +723,11 @@
       <c r="G8" s="3" t="n">
         <v>22</v>
       </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>2000000000077</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -713,6 +757,11 @@
       <c r="G9" s="3" t="n">
         <v>22</v>
       </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>2000000000084</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -742,6 +791,11 @@
       <c r="G10" s="3" t="n">
         <v>22</v>
       </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>2000000000091</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -771,6 +825,11 @@
       <c r="G11" s="3" t="n">
         <v>22</v>
       </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>2000000000107</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -800,6 +859,11 @@
       <c r="G12" s="3" t="n">
         <v>22</v>
       </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>2000000000114</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -829,6 +893,11 @@
       <c r="G13" s="3" t="n">
         <v>22</v>
       </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>2000000000121</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -858,6 +927,11 @@
       <c r="G14" s="3" t="n">
         <v>22</v>
       </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>2000000000138</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -887,6 +961,11 @@
       <c r="G15" s="3" t="n">
         <v>22</v>
       </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>2000000000145</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -916,6 +995,11 @@
       <c r="G16" s="3" t="n">
         <v>22</v>
       </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>2000000000152</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -945,6 +1029,11 @@
       <c r="G17" s="3" t="n">
         <v>22</v>
       </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>2000000000169</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -974,6 +1063,11 @@
       <c r="G18" s="3" t="n">
         <v>22</v>
       </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>2000000000176</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1003,6 +1097,11 @@
       <c r="G19" s="3" t="n">
         <v>22</v>
       </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>2000000000183</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1032,6 +1131,11 @@
       <c r="G20" s="3" t="n">
         <v>22</v>
       </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>2000000000190</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1061,6 +1165,11 @@
       <c r="G21" s="3" t="n">
         <v>22</v>
       </c>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>2000000000206</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1090,6 +1199,11 @@
       <c r="G22" s="3" t="n">
         <v>22</v>
       </c>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>2000000000213</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1119,6 +1233,11 @@
       <c r="G23" s="3" t="n">
         <v>22</v>
       </c>
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t>2000000000220</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1148,6 +1267,11 @@
       <c r="G24" s="3" t="n">
         <v>22</v>
       </c>
+      <c r="H24" s="4" t="inlineStr">
+        <is>
+          <t>2000000000237</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1177,6 +1301,11 @@
       <c r="G25" s="3" t="n">
         <v>22</v>
       </c>
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t>2000000000244</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1206,6 +1335,11 @@
       <c r="G26" s="3" t="n">
         <v>22</v>
       </c>
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>2000000000251</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1235,6 +1369,11 @@
       <c r="G27" s="3" t="n">
         <v>22</v>
       </c>
+      <c r="H27" s="4" t="inlineStr">
+        <is>
+          <t>2000000000268</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1264,6 +1403,11 @@
       <c r="G28" s="3" t="n">
         <v>4</v>
       </c>
+      <c r="H28" s="4" t="inlineStr">
+        <is>
+          <t>2000000000275</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1293,6 +1437,11 @@
       <c r="G29" s="3" t="n">
         <v>4</v>
       </c>
+      <c r="H29" s="4" t="inlineStr">
+        <is>
+          <t>2000000000282</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1322,6 +1471,11 @@
       <c r="G30" s="3" t="n">
         <v>10</v>
       </c>
+      <c r="H30" s="4" t="inlineStr">
+        <is>
+          <t>2000000000299</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1351,6 +1505,11 @@
       <c r="G31" s="3" t="n">
         <v>10</v>
       </c>
+      <c r="H31" s="4" t="inlineStr">
+        <is>
+          <t>2000000000305</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1380,6 +1539,11 @@
       <c r="G32" s="3" t="n">
         <v>10</v>
       </c>
+      <c r="H32" s="4" t="inlineStr">
+        <is>
+          <t>2000000000312</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1408,6 +1572,11 @@
       </c>
       <c r="G33" s="3" t="n">
         <v>10</v>
+      </c>
+      <c r="H33" s="4" t="inlineStr">
+        <is>
+          <t>2000000000329</t>
+        </is>
       </c>
     </row>
   </sheetData>
